--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.92</v>
@@ -4184,7 +4184,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR17" t="n">
         <v>2.37</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.77</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.36</v>
@@ -7672,7 +7672,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR33" t="n">
         <v>1.07</v>
@@ -8977,7 +8977,7 @@
         <v>0.33</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.36</v>
@@ -10070,7 +10070,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR44" t="n">
         <v>1.24</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.54</v>
@@ -12032,7 +12032,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR53" t="n">
         <v>1.56</v>
@@ -13555,7 +13555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.46</v>
@@ -15302,7 +15302,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR68" t="n">
         <v>1.94</v>
@@ -16825,7 +16825,7 @@
         <v>2.5</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ75" t="n">
         <v>2.54</v>
@@ -17264,7 +17264,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR77" t="n">
         <v>1.88</v>
@@ -19226,7 +19226,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR86" t="n">
         <v>1.37</v>
@@ -19877,7 +19877,7 @@
         <v>1.57</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.93</v>
@@ -23150,7 +23150,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR104" t="n">
         <v>1.77</v>
@@ -25327,7 +25327,7 @@
         <v>0.88</v>
       </c>
       <c r="AP114" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ114" t="n">
         <v>1</v>
@@ -26199,7 +26199,7 @@
         <v>1.22</v>
       </c>
       <c r="AP118" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.15</v>
@@ -26420,7 +26420,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR119" t="n">
         <v>2.17</v>
@@ -28161,10 +28161,10 @@
         <v>1.4</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR127" t="n">
         <v>1.62</v>
@@ -30123,7 +30123,7 @@
         <v>2.45</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ136" t="n">
         <v>2.54</v>
@@ -32742,7 +32742,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR148" t="n">
         <v>2.06</v>
@@ -33611,7 +33611,7 @@
         <v>2</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.92</v>
@@ -35216,6 +35216,224 @@
       </c>
       <c r="BP159" t="n">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>8407222</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>46081.6875</v>
+      </c>
+      <c r="F160" t="n">
+        <v>27</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S160" t="n">
+        <v>4</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X160" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -34943,13 +34943,13 @@
         <v>11</v>
       </c>
       <c r="AX158" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY158" t="n">
         <v>13</v>
       </c>
       <c r="AZ158" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA158" t="n">
         <v>9</v>
@@ -35388,13 +35388,13 @@
         <v>17</v>
       </c>
       <c r="BA160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB160" t="n">
         <v>4</v>
       </c>
       <c r="BC160" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD160" t="n">
         <v>1.57</v>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.36</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.23</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.36</v>
@@ -3094,7 +3094,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.23</v>
@@ -4617,10 +4617,10 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR19" t="n">
         <v>2.5</v>
@@ -4838,7 +4838,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR20" t="n">
         <v>1.19</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.36</v>
@@ -5710,7 +5710,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -6146,7 +6146,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR26" t="n">
         <v>1.52</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.92</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR28" t="n">
         <v>1.93</v>
@@ -7018,7 +7018,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR30" t="n">
         <v>1.78</v>
@@ -7454,7 +7454,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR32" t="n">
         <v>2.08</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
         <v>1</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.54</v>
@@ -10503,10 +10503,10 @@
         <v>2.33</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR46" t="n">
         <v>1.62</v>
@@ -10721,7 +10721,7 @@
         <v>1.33</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.93</v>
@@ -10942,7 +10942,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR48" t="n">
         <v>1.09</v>
@@ -11160,7 +11160,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR49" t="n">
         <v>1.81</v>
@@ -11814,7 +11814,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR52" t="n">
         <v>1.37</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.23</v>
@@ -12247,7 +12247,7 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.92</v>
@@ -13558,7 +13558,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR60" t="n">
         <v>1.88</v>
@@ -13773,10 +13773,10 @@
         <v>1.8</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR61" t="n">
         <v>1.75</v>
@@ -14427,7 +14427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.23</v>
@@ -14648,7 +14648,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR65" t="n">
         <v>2.48</v>
@@ -15081,7 +15081,7 @@
         <v>1.4</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.93</v>
@@ -16171,10 +16171,10 @@
         <v>1.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR72" t="n">
         <v>1.74</v>
@@ -17046,7 +17046,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR76" t="n">
         <v>2.3</v>
@@ -17261,7 +17261,7 @@
         <v>1.83</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.23</v>
@@ -17915,7 +17915,7 @@
         <v>0.17</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.36</v>
@@ -18136,7 +18136,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR81" t="n">
         <v>1.87</v>
@@ -18354,7 +18354,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR82" t="n">
         <v>1.54</v>
@@ -18787,10 +18787,10 @@
         <v>1.43</v>
       </c>
       <c r="AP84" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR84" t="n">
         <v>1.53</v>
@@ -20095,7 +20095,7 @@
         <v>2.57</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ90" t="n">
         <v>2.54</v>
@@ -20531,7 +20531,7 @@
         <v>1</v>
       </c>
       <c r="AP92" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.23</v>
@@ -20970,7 +20970,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR94" t="n">
         <v>1.87</v>
@@ -21188,7 +21188,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR95" t="n">
         <v>1.17</v>
@@ -21621,10 +21621,10 @@
         <v>1.29</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR97" t="n">
         <v>1.78</v>
@@ -22493,7 +22493,7 @@
         <v>1.38</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.36</v>
@@ -23583,7 +23583,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.77</v>
@@ -23804,7 +23804,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR107" t="n">
         <v>1.61</v>
@@ -24022,7 +24022,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR108" t="n">
         <v>1.95</v>
@@ -24240,7 +24240,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR109" t="n">
         <v>2.04</v>
@@ -24673,7 +24673,7 @@
         <v>1.22</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.36</v>
@@ -25109,7 +25109,7 @@
         <v>2</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.92</v>
@@ -25766,7 +25766,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR116" t="n">
         <v>1.64</v>
@@ -25981,7 +25981,7 @@
         <v>1.11</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ117" t="n">
         <v>1</v>
@@ -26202,7 +26202,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR118" t="n">
         <v>1.61</v>
@@ -26635,7 +26635,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ120" t="n">
         <v>2.54</v>
@@ -26853,7 +26853,7 @@
         <v>0.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.77</v>
@@ -27728,7 +27728,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR125" t="n">
         <v>1.89</v>
@@ -28597,10 +28597,10 @@
         <v>1.6</v>
       </c>
       <c r="AP129" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR129" t="n">
         <v>1.45</v>
@@ -29251,10 +29251,10 @@
         <v>1.2</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR132" t="n">
         <v>1.58</v>
@@ -29690,7 +29690,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR134" t="n">
         <v>1.32</v>
@@ -29905,7 +29905,7 @@
         <v>1.09</v>
       </c>
       <c r="AP135" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.93</v>
@@ -30344,7 +30344,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR137" t="n">
         <v>2.11</v>
@@ -30559,7 +30559,7 @@
         <v>2</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.92</v>
@@ -31870,7 +31870,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR144" t="n">
         <v>1.54</v>
@@ -32521,7 +32521,7 @@
         <v>0.42</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.36</v>
@@ -32960,7 +32960,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR149" t="n">
         <v>2.07</v>
@@ -33175,7 +33175,7 @@
         <v>1.25</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.23</v>
@@ -33829,10 +33829,10 @@
         <v>1</v>
       </c>
       <c r="AP153" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR153" t="n">
         <v>1.44</v>
@@ -34268,7 +34268,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR155" t="n">
         <v>1.64</v>
@@ -35434,6 +35434,660 @@
       </c>
       <c r="BP160" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>8407221</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>46082.41666666666</v>
+      </c>
+      <c r="F161" t="n">
+        <v>27</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+      <c r="N161" t="n">
+        <v>3</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>['1', '68']</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S161" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U161" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X161" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>8407224</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>46082.52083333334</v>
+      </c>
+      <c r="F162" t="n">
+        <v>27</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>3</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>3</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['64', '71', '86']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S162" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U162" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X162" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>36</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>8407225</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>46082.52083333334</v>
+      </c>
+      <c r="F163" t="n">
+        <v>27</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S163" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X163" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -36024,7 +36024,7 @@
         <v>3.12</v>
       </c>
       <c r="AU163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV163" t="n">
         <v>4</v>
@@ -36036,7 +36036,7 @@
         <v>12</v>
       </c>
       <c r="AY163" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ163" t="n">
         <v>16</v>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -34943,13 +34943,13 @@
         <v>11</v>
       </c>
       <c r="AX158" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY158" t="n">
         <v>13</v>
       </c>
       <c r="AZ158" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA158" t="n">
         <v>9</v>
@@ -35376,13 +35376,13 @@
         <v>4</v>
       </c>
       <c r="AW160" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX160" t="n">
         <v>13</v>
       </c>
       <c r="AY160" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ160" t="n">
         <v>17</v>
@@ -35812,13 +35812,13 @@
         <v>1</v>
       </c>
       <c r="AW162" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX162" t="n">
         <v>5</v>
       </c>
       <c r="AY162" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AZ162" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.54</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.07</v>
@@ -3530,7 +3530,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR14" t="n">
         <v>2.11</v>
@@ -3963,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
         <v>2.54</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR17" t="n">
         <v>2.37</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.64</v>
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ21" t="n">
         <v>2.54</v>
@@ -5707,7 +5707,7 @@
         <v>2</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.07</v>
@@ -7233,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR31" t="n">
         <v>1.6</v>
@@ -7669,10 +7669,10 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR33" t="n">
         <v>1.07</v>
@@ -7887,10 +7887,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR34" t="n">
         <v>1.27</v>
@@ -8108,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR35" t="n">
         <v>1.67</v>
@@ -8326,7 +8326,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR37" t="n">
         <v>1.46</v>
@@ -8759,7 +8759,7 @@
         <v>0.67</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.77</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.92</v>
@@ -9634,7 +9634,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR42" t="n">
         <v>1.11</v>
@@ -10067,10 +10067,10 @@
         <v>2.33</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR44" t="n">
         <v>1.24</v>
@@ -10724,7 +10724,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR47" t="n">
         <v>1.67</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.36</v>
@@ -11378,7 +11378,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR50" t="n">
         <v>1.87</v>
@@ -11811,7 +11811,7 @@
         <v>1.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.07</v>
@@ -12032,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR53" t="n">
         <v>1.56</v>
@@ -12465,10 +12465,10 @@
         <v>0.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR55" t="n">
         <v>1.29</v>
@@ -13119,7 +13119,7 @@
         <v>2.5</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.36</v>
@@ -13337,10 +13337,10 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR59" t="n">
         <v>1.96</v>
@@ -14430,7 +14430,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR64" t="n">
         <v>1.88</v>
@@ -14863,7 +14863,7 @@
         <v>2.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.36</v>
@@ -15084,7 +15084,7 @@
         <v>1</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR67" t="n">
         <v>1.44</v>
@@ -15302,7 +15302,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR68" t="n">
         <v>1.94</v>
@@ -15517,10 +15517,10 @@
         <v>1.2</v>
       </c>
       <c r="AP69" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR69" t="n">
         <v>1.12</v>
@@ -15735,10 +15735,10 @@
         <v>0.6</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR70" t="n">
         <v>1.96</v>
@@ -15953,7 +15953,7 @@
         <v>0.4</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.77</v>
@@ -16389,7 +16389,7 @@
         <v>1.83</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.36</v>
@@ -16607,7 +16607,7 @@
         <v>0.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.77</v>
@@ -17264,7 +17264,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR77" t="n">
         <v>1.88</v>
@@ -17482,7 +17482,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR78" t="n">
         <v>1.93</v>
@@ -17697,10 +17697,10 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR79" t="n">
         <v>1.46</v>
@@ -18572,7 +18572,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR83" t="n">
         <v>1.95</v>
@@ -19005,7 +19005,7 @@
         <v>1.8</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.92</v>
@@ -19223,10 +19223,10 @@
         <v>1.71</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR86" t="n">
         <v>1.37</v>
@@ -19441,7 +19441,7 @@
         <v>0.71</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.77</v>
@@ -19659,7 +19659,7 @@
         <v>0.14</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.36</v>
@@ -19880,7 +19880,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR89" t="n">
         <v>1.76</v>
@@ -20534,7 +20534,7 @@
         <v>1</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR92" t="n">
         <v>1.54</v>
@@ -21185,7 +21185,7 @@
         <v>1.38</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.64</v>
@@ -21406,7 +21406,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR96" t="n">
         <v>1.58</v>
@@ -21839,7 +21839,7 @@
         <v>0.5</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.36</v>
@@ -22711,10 +22711,10 @@
         <v>1.25</v>
       </c>
       <c r="AP102" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR102" t="n">
         <v>1.35</v>
@@ -22932,7 +22932,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR103" t="n">
         <v>2.24</v>
@@ -23150,7 +23150,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR104" t="n">
         <v>1.77</v>
@@ -23365,7 +23365,7 @@
         <v>2.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ105" t="n">
         <v>2.54</v>
@@ -23801,7 +23801,7 @@
         <v>1.56</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.64</v>
@@ -24019,7 +24019,7 @@
         <v>1.25</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.36</v>
@@ -24458,7 +24458,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR110" t="n">
         <v>2.26</v>
@@ -24891,10 +24891,10 @@
         <v>1.33</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR112" t="n">
         <v>1.33</v>
@@ -25330,7 +25330,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR114" t="n">
         <v>1.69</v>
@@ -25763,7 +25763,7 @@
         <v>1.44</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.36</v>
@@ -25984,7 +25984,7 @@
         <v>2</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR117" t="n">
         <v>1.65</v>
@@ -26420,7 +26420,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR119" t="n">
         <v>2.17</v>
@@ -27071,7 +27071,7 @@
         <v>0.5</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.36</v>
@@ -27510,7 +27510,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR124" t="n">
         <v>2.08</v>
@@ -27725,7 +27725,7 @@
         <v>1.7</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.64</v>
@@ -27946,7 +27946,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR126" t="n">
         <v>1.82</v>
@@ -28164,7 +28164,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR127" t="n">
         <v>1.62</v>
@@ -28379,10 +28379,10 @@
         <v>1.3</v>
       </c>
       <c r="AP128" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR128" t="n">
         <v>1.28</v>
@@ -28815,7 +28815,7 @@
         <v>2.11</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.92</v>
@@ -29687,7 +29687,7 @@
         <v>1.55</v>
       </c>
       <c r="AP134" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ134" t="n">
         <v>1.36</v>
@@ -29908,7 +29908,7 @@
         <v>1</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR135" t="n">
         <v>1.44</v>
@@ -30777,7 +30777,7 @@
         <v>0.82</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.77</v>
@@ -30995,10 +30995,10 @@
         <v>1.27</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR140" t="n">
         <v>1.39</v>
@@ -31213,7 +31213,7 @@
         <v>0.45</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.36</v>
@@ -31434,7 +31434,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR142" t="n">
         <v>1.81</v>
@@ -31652,7 +31652,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR143" t="n">
         <v>2.06</v>
@@ -32085,7 +32085,7 @@
         <v>1.33</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.36</v>
@@ -32742,7 +32742,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR148" t="n">
         <v>2.06</v>
@@ -33178,7 +33178,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR150" t="n">
         <v>1.77</v>
@@ -33393,7 +33393,7 @@
         <v>1.91</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.92</v>
@@ -34050,7 +34050,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR154" t="n">
         <v>1.59</v>
@@ -34265,7 +34265,7 @@
         <v>1.67</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.64</v>
@@ -34483,10 +34483,10 @@
         <v>1.08</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR156" t="n">
         <v>1.31</v>
@@ -34701,7 +34701,7 @@
         <v>2.5</v>
       </c>
       <c r="AP157" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ157" t="n">
         <v>2.54</v>
@@ -35358,7 +35358,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR160" t="n">
         <v>1.55</v>
@@ -36088,6 +36088,878 @@
       </c>
       <c r="BP163" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>8407226</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>46084.6875</v>
+      </c>
+      <c r="F164" t="n">
+        <v>28</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S164" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U164" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V164" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X164" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>8407230</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>46085.6875</v>
+      </c>
+      <c r="F165" t="n">
+        <v>28</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>2</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" t="n">
+        <v>3</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>['12', '62']</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S165" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U165" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V165" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X165" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>8407229</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>46085.6875</v>
+      </c>
+      <c r="F166" t="n">
+        <v>28</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="n">
+        <v>2</v>
+      </c>
+      <c r="N166" t="n">
+        <v>3</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>['56', '79']</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R166" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S166" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U166" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V166" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X166" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>8407227</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>46085.6875</v>
+      </c>
+      <c r="F167" t="n">
+        <v>28</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>3</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>['35', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S167" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U167" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V167" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X167" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP167"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.14</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.07</v>
@@ -4402,7 +4402,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR18" t="n">
         <v>1.59</v>
@@ -5925,10 +5925,10 @@
         <v>0.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR25" t="n">
         <v>1.52</v>
@@ -6364,7 +6364,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.64</v>
@@ -8762,7 +8762,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR38" t="n">
         <v>1.4</v>
@@ -9198,7 +9198,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR40" t="n">
         <v>1.62</v>
@@ -9849,7 +9849,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.36</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.21</v>
@@ -11593,7 +11593,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.36</v>
@@ -12250,7 +12250,7 @@
         <v>2</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR54" t="n">
         <v>1.78</v>
@@ -12904,7 +12904,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR57" t="n">
         <v>1.87</v>
@@ -13994,7 +13994,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR62" t="n">
         <v>1.47</v>
@@ -14209,7 +14209,7 @@
         <v>0.2</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.36</v>
@@ -14645,7 +14645,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.07</v>
@@ -15299,7 +15299,7 @@
         <v>2.2</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.14</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR71" t="n">
         <v>1.4</v>
@@ -16610,7 +16610,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR74" t="n">
         <v>1.12</v>
@@ -17043,7 +17043,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.36</v>
@@ -18133,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.36</v>
@@ -19008,7 +19008,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR85" t="n">
         <v>1.33</v>
@@ -19444,7 +19444,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR87" t="n">
         <v>1.95</v>
@@ -20313,10 +20313,10 @@
         <v>2</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR91" t="n">
         <v>2.27</v>
@@ -20749,7 +20749,7 @@
         <v>1.57</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.36</v>
@@ -22060,7 +22060,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR99" t="n">
         <v>1.57</v>
@@ -22275,10 +22275,10 @@
         <v>1.86</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR100" t="n">
         <v>2.09</v>
@@ -22929,7 +22929,7 @@
         <v>0.86</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.14</v>
@@ -23586,7 +23586,7 @@
         <v>2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR106" t="n">
         <v>1.67</v>
@@ -24237,7 +24237,7 @@
         <v>1.38</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.07</v>
@@ -24455,7 +24455,7 @@
         <v>1.11</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.21</v>
@@ -25112,7 +25112,7 @@
         <v>1</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR113" t="n">
         <v>1.52</v>
@@ -26417,7 +26417,7 @@
         <v>1.44</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.14</v>
@@ -26856,7 +26856,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR121" t="n">
         <v>1.82</v>
@@ -27507,7 +27507,7 @@
         <v>1.2</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.07</v>
@@ -28818,7 +28818,7 @@
         <v>1</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR130" t="n">
         <v>1.63</v>
@@ -29033,7 +29033,7 @@
         <v>2.4</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ131" t="n">
         <v>2.54</v>
@@ -30341,7 +30341,7 @@
         <v>1.09</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.07</v>
@@ -30562,7 +30562,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR138" t="n">
         <v>1.75</v>
@@ -30780,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR139" t="n">
         <v>1.61</v>
@@ -31649,7 +31649,7 @@
         <v>1.18</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.14</v>
@@ -32306,7 +32306,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR146" t="n">
         <v>1.84</v>
@@ -32739,7 +32739,7 @@
         <v>1.36</v>
       </c>
       <c r="AP148" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.14</v>
@@ -32957,7 +32957,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.36</v>
@@ -33396,7 +33396,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR151" t="n">
         <v>1.3</v>
@@ -33614,7 +33614,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR152" t="n">
         <v>1.57</v>
@@ -34919,7 +34919,7 @@
         <v>1.46</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.36</v>
@@ -36899,13 +36899,13 @@
         <v>1</v>
       </c>
       <c r="AV167" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW167" t="n">
         <v>10</v>
       </c>
       <c r="AX167" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY167" t="n">
         <v>11</v>
@@ -36960,6 +36960,442 @@
       </c>
       <c r="BP167" t="n">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>8407228</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>46086.6875</v>
+      </c>
+      <c r="F168" t="n">
+        <v>28</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" t="n">
+        <v>2</v>
+      </c>
+      <c r="N168" t="n">
+        <v>4</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>['55', '62']</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>['37', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R168" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S168" t="n">
+        <v>4</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U168" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V168" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X168" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>8407232</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>46086.6875</v>
+      </c>
+      <c r="F169" t="n">
+        <v>28</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S169" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U169" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V169" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X169" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -36681,13 +36681,13 @@
         <v>2</v>
       </c>
       <c r="AV166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW166" t="n">
         <v>8</v>
       </c>
       <c r="AX166" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY166" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.54</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.86</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.36</v>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.71</v>
@@ -4620,7 +4620,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
         <v>2.5</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.64</v>
@@ -5274,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR22" t="n">
         <v>1.7</v>
@@ -5492,7 +5492,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR23" t="n">
         <v>1.97</v>
@@ -5710,7 +5710,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.64</v>
@@ -6797,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR29" t="n">
         <v>1.79</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.21</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.14</v>
@@ -8759,7 +8759,7 @@
         <v>0.67</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.71</v>
@@ -8977,10 +8977,10 @@
         <v>0.33</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR39" t="n">
         <v>1.89</v>
@@ -9631,7 +9631,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.14</v>
@@ -9852,7 +9852,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR43" t="n">
         <v>2.38</v>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR46" t="n">
         <v>1.62</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.64</v>
@@ -11596,7 +11596,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR51" t="n">
         <v>2.4</v>
@@ -11811,10 +11811,10 @@
         <v>1.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR52" t="n">
         <v>1.37</v>
@@ -12683,7 +12683,7 @@
         <v>2.4</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ56" t="n">
         <v>2.54</v>
@@ -13122,7 +13122,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR58" t="n">
         <v>1.1</v>
@@ -13555,7 +13555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.36</v>
@@ -13991,7 +13991,7 @@
         <v>2.25</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.86</v>
@@ -14212,7 +14212,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR63" t="n">
         <v>1.87</v>
@@ -14648,7 +14648,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR65" t="n">
         <v>2.48</v>
@@ -14863,10 +14863,10 @@
         <v>2.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR66" t="n">
         <v>1.4</v>
@@ -16392,7 +16392,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR73" t="n">
         <v>1.92</v>
@@ -16825,7 +16825,7 @@
         <v>2.5</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ75" t="n">
         <v>2.54</v>
@@ -17918,7 +17918,7 @@
         <v>2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR80" t="n">
         <v>1.64</v>
@@ -18351,10 +18351,10 @@
         <v>1.17</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR82" t="n">
         <v>1.54</v>
@@ -19005,7 +19005,7 @@
         <v>1.8</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.86</v>
@@ -19223,7 +19223,7 @@
         <v>1.71</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.14</v>
@@ -19662,7 +19662,7 @@
         <v>1</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR88" t="n">
         <v>1.45</v>
@@ -19877,7 +19877,7 @@
         <v>1.57</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.07</v>
@@ -20752,7 +20752,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR93" t="n">
         <v>1.97</v>
@@ -20970,7 +20970,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR94" t="n">
         <v>1.87</v>
@@ -21403,7 +21403,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.07</v>
@@ -21842,7 +21842,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR98" t="n">
         <v>1.94</v>
@@ -22057,7 +22057,7 @@
         <v>0.63</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.71</v>
@@ -22496,7 +22496,7 @@
         <v>2</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR101" t="n">
         <v>1.69</v>
@@ -22711,7 +22711,7 @@
         <v>1.25</v>
       </c>
       <c r="AP102" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.21</v>
@@ -24240,7 +24240,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR109" t="n">
         <v>2.04</v>
@@ -24676,7 +24676,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR111" t="n">
         <v>1.8</v>
@@ -24891,7 +24891,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.07</v>
@@ -25327,7 +25327,7 @@
         <v>0.88</v>
       </c>
       <c r="AP114" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.14</v>
@@ -25545,10 +25545,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR115" t="n">
         <v>1.56</v>
@@ -26199,10 +26199,10 @@
         <v>1.22</v>
       </c>
       <c r="AP118" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR118" t="n">
         <v>1.61</v>
@@ -27071,10 +27071,10 @@
         <v>0.5</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR122" t="n">
         <v>1.32</v>
@@ -27289,10 +27289,10 @@
         <v>1.4</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR123" t="n">
         <v>1.57</v>
@@ -28161,7 +28161,7 @@
         <v>1.4</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.14</v>
@@ -29254,7 +29254,7 @@
         <v>2</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR132" t="n">
         <v>1.58</v>
@@ -29469,10 +29469,10 @@
         <v>1.36</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR133" t="n">
         <v>1.56</v>
@@ -30123,7 +30123,7 @@
         <v>2.45</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ136" t="n">
         <v>2.54</v>
@@ -30344,7 +30344,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR137" t="n">
         <v>2.11</v>
@@ -30995,7 +30995,7 @@
         <v>1.27</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.21</v>
@@ -31216,7 +31216,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR141" t="n">
         <v>1.92</v>
@@ -31867,7 +31867,7 @@
         <v>1.82</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.64</v>
@@ -32088,7 +32088,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR145" t="n">
         <v>1.87</v>
@@ -32524,7 +32524,7 @@
         <v>2</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR147" t="n">
         <v>1.67</v>
@@ -33611,7 +33611,7 @@
         <v>2</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.86</v>
@@ -33832,7 +33832,7 @@
         <v>1</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR153" t="n">
         <v>1.44</v>
@@ -34047,7 +34047,7 @@
         <v>1</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.07</v>
@@ -34483,7 +34483,7 @@
         <v>1.08</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.14</v>
@@ -34922,7 +34922,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR158" t="n">
         <v>2.08</v>
@@ -35140,7 +35140,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR159" t="n">
         <v>1.8</v>
@@ -35355,7 +35355,7 @@
         <v>1.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.14</v>
@@ -35794,7 +35794,7 @@
         <v>2</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR162" t="n">
         <v>1.75</v>
@@ -36445,7 +36445,7 @@
         <v>1.23</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.14</v>
@@ -37396,6 +37396,660 @@
       </c>
       <c r="BP169" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>8407231</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>46088.58333333334</v>
+      </c>
+      <c r="F170" t="n">
+        <v>29</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R170" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S170" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U170" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V170" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X170" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>8407233</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>46088.58333333334</v>
+      </c>
+      <c r="F171" t="n">
+        <v>29</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>3</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>['2', '88']</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S171" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U171" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X171" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>8407234</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>46088.6875</v>
+      </c>
+      <c r="F172" t="n">
+        <v>29</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>3</v>
+      </c>
+      <c r="N172" t="n">
+        <v>4</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>['44', '63', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R172" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S172" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V172" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X172" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Switzerland Super League_20252026.xlsx
@@ -37338,16 +37338,16 @@
         <v>5</v>
       </c>
       <c r="AW169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX169" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY169" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ169" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA169" t="n">
         <v>4</v>
